--- a/samples/Sample_10_For_Large_Scale_100_Students.xlsx
+++ b/samples/Sample_10_For_Large_Scale_100_Students.xlsx
@@ -9,16 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 3" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 5" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 6" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 8" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 9" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Test 10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 8" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 9" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUC2A-Monthly Test 10" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
@@ -643,7 +643,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Monthly Test 1</t>
+          <t>PUC2A-Monthly Test 1</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Monthly Test 2</t>
+          <t>PUC2A-Monthly Test 2</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Monthly Test 3</t>
+          <t>PUC2A-Monthly Test 3</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Monthly Test 4</t>
+          <t>PUC2A-Monthly Test 4</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Monthly Test 5</t>
+          <t>PUC2A-Monthly Test 5</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Monthly Test 6</t>
+          <t>PUC2A-Monthly Test 6</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Monthly Test 7</t>
+          <t>PUC2A-Monthly Test 7</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Monthly Test 8</t>
+          <t>PUC2A-Monthly Test 8</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Monthly Test 9</t>
+          <t>PUC2A-Monthly Test 9</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Monthly Test 10</t>
+          <t>PUC2A-Monthly Test 10</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1537,7 +1536,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -1573,7 +1571,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1604,7 +1601,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1630,8 +1626,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1657,8 +1651,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1689,7 +1681,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1720,7 +1711,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1751,7 +1741,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1782,7 +1771,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1843,8 +1831,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1870,8 +1856,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1937,7 +1921,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1963,7 +1946,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -2029,7 +2011,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -2065,7 +2046,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2091,8 +2071,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2158,7 +2136,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2189,7 +2166,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2285,8 +2261,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2312,8 +2286,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2344,7 +2316,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2375,7 +2346,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2406,7 +2376,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2437,7 +2406,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2468,7 +2436,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2499,7 +2466,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2525,7 +2491,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -2561,7 +2526,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2592,7 +2556,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2623,7 +2586,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2654,7 +2616,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2685,7 +2646,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2711,8 +2671,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2743,7 +2701,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2769,8 +2726,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2801,7 +2756,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2832,7 +2786,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2858,8 +2811,6 @@
       <c r="G46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2890,7 +2841,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2921,7 +2871,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2952,7 +2901,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2978,8 +2926,6 @@
       <c r="G50" t="n">
         <v>2</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3010,7 +2956,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3041,7 +2986,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3102,8 +3046,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3134,7 +3076,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3160,8 +3101,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3222,8 +3161,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3254,7 +3191,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3280,8 +3216,6 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3312,7 +3246,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3373,8 +3306,6 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3405,7 +3336,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3436,7 +3366,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3467,7 +3396,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3498,7 +3426,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3529,7 +3456,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3555,7 +3481,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -3621,7 +3546,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -3692,7 +3616,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3723,7 +3646,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3754,7 +3676,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3780,8 +3701,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3807,8 +3726,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3839,7 +3756,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3870,7 +3786,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3896,7 +3811,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -3932,7 +3846,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3963,7 +3876,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3994,7 +3906,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4025,7 +3936,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4056,7 +3966,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4087,7 +3996,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4118,7 +4026,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4144,8 +4051,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4171,7 +4076,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -4237,8 +4141,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4269,7 +4171,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4300,7 +4201,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4331,7 +4231,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4362,7 +4261,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4388,8 +4286,6 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4415,8 +4311,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4447,7 +4341,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4478,7 +4371,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4651,7 +4543,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4677,8 +4568,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4709,7 +4598,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4735,7 +4623,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -4766,7 +4653,6 @@
       <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -4802,7 +4688,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4828,7 +4713,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -4894,8 +4778,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4961,7 +4843,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4987,7 +4868,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5018,8 +4898,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5045,8 +4923,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5077,7 +4953,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5103,8 +4978,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5170,7 +5043,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5196,7 +5068,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -5227,8 +5098,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5294,7 +5163,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5360,7 +5228,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5386,8 +5253,6 @@
       <c r="G26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5418,7 +5283,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5449,7 +5313,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5480,7 +5343,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5511,7 +5373,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5542,7 +5403,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5573,7 +5433,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5604,7 +5463,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5635,7 +5493,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5666,7 +5523,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5697,7 +5553,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5763,7 +5618,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5789,8 +5643,6 @@
       <c r="G39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5816,8 +5668,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5848,7 +5698,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5909,8 +5758,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5941,7 +5788,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5972,7 +5818,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5998,8 +5843,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6025,8 +5868,6 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6057,7 +5898,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6083,8 +5923,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6115,7 +5953,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6141,8 +5978,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6173,7 +6008,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6309,7 +6143,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6340,7 +6173,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6371,7 +6203,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6397,8 +6228,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6429,7 +6258,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6490,7 +6318,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -6526,7 +6353,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6552,8 +6378,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6579,7 +6403,6 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -6650,7 +6473,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6681,7 +6503,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6712,7 +6533,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6778,7 +6598,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6809,7 +6628,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6875,7 +6693,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6906,7 +6723,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6967,8 +6783,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6999,7 +6813,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7030,7 +6843,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7061,7 +6873,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7087,8 +6898,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7119,7 +6928,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7150,7 +6958,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7181,7 +6988,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7212,7 +7018,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7243,7 +7048,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7274,7 +7078,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7300,7 +7103,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -7336,7 +7138,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7367,7 +7168,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7393,8 +7193,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7425,7 +7223,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7456,7 +7253,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7482,8 +7278,6 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7514,7 +7308,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7545,7 +7338,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7606,8 +7398,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7638,7 +7428,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7669,7 +7458,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7695,7 +7483,6 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -8043,7 +7830,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -8179,7 +7965,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -8245,7 +8030,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
@@ -8276,7 +8060,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -8377,7 +8160,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -8408,7 +8190,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -8439,7 +8220,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Was doing well earlier, something seems to be affecting focus now.</t>
@@ -8470,7 +8250,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Was doing well earlier, something seems to be affecting focus now.</t>
@@ -8571,7 +8350,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -8602,7 +8380,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -8668,7 +8445,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -8699,7 +8475,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -8765,7 +8540,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -8831,7 +8605,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -8862,7 +8635,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -9068,7 +8840,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -9204,7 +8975,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -9235,7 +9005,6 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -9266,7 +9035,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Was doing well earlier, something seems to be affecting focus now.</t>
@@ -9367,7 +9135,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Ups and downs need to be understood — talk to student directly.</t>
@@ -9573,7 +9340,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -9604,7 +9370,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -9950,7 +9715,6 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -10051,7 +9815,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -10152,7 +9915,6 @@
       <c r="G72" t="n">
         <v>2</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Needs attention — performance has slipped recently.</t>
@@ -10358,7 +10120,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -10599,7 +10360,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -10630,7 +10390,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -10661,7 +10420,6 @@
       <c r="G87" t="n">
         <v>0</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -10692,7 +10450,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -10758,7 +10515,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
@@ -10824,7 +10580,6 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -11030,7 +10785,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Ups and downs need to be understood — talk to student directly.</t>
@@ -13040,8 +12794,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13072,7 +12824,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13103,7 +12854,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13134,7 +12884,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13200,7 +12949,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13231,7 +12979,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13262,7 +13009,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13293,7 +13039,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13359,7 +13104,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13385,8 +13129,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13412,8 +13154,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13444,7 +13184,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13510,7 +13249,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13536,8 +13274,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13568,7 +13304,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13594,8 +13329,6 @@
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13621,8 +13354,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13653,7 +13384,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13684,7 +13414,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13750,7 +13479,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13776,8 +13504,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13808,7 +13534,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13909,7 +13634,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13970,8 +13694,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14002,7 +13724,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14063,8 +13784,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14165,7 +13884,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14191,8 +13909,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14223,7 +13939,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14254,7 +13969,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14285,7 +13999,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14316,7 +14029,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14342,8 +14054,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14374,7 +14084,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14400,8 +14109,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14432,7 +14139,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14458,8 +14164,6 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14490,7 +14194,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14516,8 +14219,6 @@
       <c r="G50" t="n">
         <v>2</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14548,7 +14249,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14609,8 +14309,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14671,8 +14369,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14703,7 +14399,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14734,7 +14429,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -14760,8 +14454,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14792,7 +14484,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -14858,7 +14549,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -14889,7 +14579,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -14920,7 +14609,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -14951,7 +14639,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -14977,7 +14664,6 @@
       <c r="G65" t="n">
         <v>1</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -15013,7 +14699,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15079,7 +14764,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15175,8 +14859,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15202,7 +14884,6 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Was doing well earlier, something seems to be affecting focus now.</t>
@@ -15273,7 +14954,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15299,8 +14979,6 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -15331,7 +15009,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -15362,7 +15039,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -15428,7 +15104,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15454,8 +15129,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15486,7 +15159,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15552,7 +15224,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15578,8 +15249,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -15605,8 +15274,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -15632,8 +15299,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -15664,7 +15329,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -15690,8 +15354,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -15722,7 +15384,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -15753,7 +15414,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -15779,7 +15439,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -15815,7 +15474,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15846,7 +15504,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15877,7 +15534,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15908,7 +15564,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16044,7 +15699,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16075,7 +15729,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16106,7 +15759,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16209,7 +15861,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16235,8 +15886,6 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16267,7 +15916,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16363,8 +16011,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16395,7 +16041,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16421,8 +16066,6 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16488,7 +16131,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16519,7 +16161,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16545,7 +16186,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -16576,8 +16216,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16608,7 +16246,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16639,7 +16276,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16665,7 +16301,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Needs urgent academic support, at risk of failing.</t>
@@ -16696,8 +16331,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16728,7 +16361,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16754,8 +16386,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16781,8 +16411,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16813,7 +16441,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16844,7 +16471,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16875,7 +16501,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16936,7 +16561,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -16967,8 +16591,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16994,8 +16616,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17026,7 +16646,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17057,7 +16676,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17083,8 +16701,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17115,7 +16731,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17146,7 +16761,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17172,7 +16786,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -17208,7 +16821,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17234,7 +16846,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -17265,8 +16876,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17292,7 +16901,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -17328,7 +16936,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17359,7 +16966,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17390,7 +16996,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17421,7 +17026,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17452,7 +17056,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17483,7 +17086,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17514,7 +17116,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17545,7 +17146,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17571,8 +17171,6 @@
       <c r="G47" t="n">
         <v>2</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17598,7 +17196,6 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Unpredictable performance, may help to identify what's different on good days.</t>
@@ -17629,8 +17226,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17656,8 +17251,6 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17683,8 +17276,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17715,7 +17306,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17746,7 +17336,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17772,8 +17361,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17799,8 +17386,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17826,8 +17411,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17858,7 +17441,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17884,8 +17466,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17911,7 +17491,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -18017,7 +17596,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18043,8 +17621,6 @@
       <c r="G63" t="n">
         <v>0</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18075,7 +17651,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18106,7 +17681,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18172,7 +17746,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18203,7 +17776,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18234,7 +17806,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18260,8 +17831,6 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18327,7 +17896,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18358,7 +17926,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18389,7 +17956,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18420,7 +17986,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18486,7 +18051,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18547,8 +18111,6 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18609,8 +18171,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18641,7 +18201,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18667,8 +18226,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18699,7 +18256,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18730,7 +18286,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18761,7 +18316,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18787,7 +18341,6 @@
       <c r="G87" t="n">
         <v>2</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -18823,7 +18376,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18924,7 +18476,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18950,8 +18501,6 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18982,7 +18531,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19013,7 +18561,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19079,7 +18626,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19110,7 +18656,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19176,7 +18721,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19207,7 +18751,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19238,7 +18781,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19341,7 +18883,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19367,8 +18908,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19394,7 +18933,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -19430,7 +18968,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19456,8 +18993,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19483,8 +19018,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19515,7 +19048,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19581,7 +19113,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19607,8 +19138,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19669,8 +19198,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19701,7 +19228,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19727,8 +19253,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19759,7 +19283,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19785,8 +19308,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19812,7 +19333,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Needs urgent academic support, at risk of failing.</t>
@@ -19878,7 +19398,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -19909,7 +19428,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -19945,7 +19463,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19976,7 +19493,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20007,7 +19523,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20038,7 +19553,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20104,7 +19618,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20165,8 +19678,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20197,7 +19708,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20228,7 +19738,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -20259,7 +19768,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -20285,8 +19793,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -20317,7 +19823,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20343,8 +19848,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20375,7 +19878,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20406,7 +19908,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20432,8 +19933,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20464,7 +19963,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20490,8 +19988,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20557,7 +20053,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20653,8 +20148,6 @@
       <c r="G45" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20680,7 +20173,6 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -20716,7 +20208,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20782,7 +20273,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20813,7 +20303,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20844,7 +20333,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20870,7 +20358,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Consistently excellent — ready for tougher challenges.</t>
@@ -21011,7 +20498,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21037,7 +20523,6 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -21108,7 +20593,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21174,7 +20658,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21200,8 +20683,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21232,7 +20713,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21298,7 +20778,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21364,7 +20843,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21430,7 +20908,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21461,7 +20938,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21527,7 +21003,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -21558,7 +21033,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21624,7 +21098,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21655,7 +21128,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21686,7 +21158,6 @@
           <t>Differential Equations</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21712,8 +21183,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21739,8 +21208,6 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21766,8 +21233,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -21798,7 +21263,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21829,7 +21293,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21860,7 +21323,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21886,8 +21348,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21918,7 +21378,6 @@
           <t>Integrals</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21984,7 +21443,6 @@
           <t>Matrices</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22015,7 +21473,6 @@
           <t>Applications of Derivatives</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22046,7 +21503,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22072,8 +21528,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22169,8 +21623,6 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22236,7 +21688,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -22267,7 +21718,6 @@
           <t>Relations &amp; Functions</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -22293,8 +21743,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -22360,7 +21808,6 @@
           <t>Continuity &amp; Differentiability</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -22528,8 +21975,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22560,7 +22005,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22591,7 +22035,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22657,7 +22100,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22688,7 +22130,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22719,7 +22160,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22750,7 +22190,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22776,7 +22215,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -22812,7 +22250,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22843,7 +22280,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22869,7 +22305,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -22975,7 +22410,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23006,7 +22440,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23032,7 +22465,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -23063,8 +22495,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23090,8 +22520,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23122,7 +22550,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -23153,7 +22580,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -23184,7 +22610,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23210,8 +22635,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23237,8 +22660,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -23269,7 +22690,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -23300,7 +22720,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -23331,7 +22750,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23357,8 +22775,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23384,7 +22800,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -23415,8 +22830,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -23447,7 +22860,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -23478,7 +22890,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -23544,7 +22955,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -23575,7 +22985,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -23636,8 +23045,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23663,8 +23070,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23695,7 +23100,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -23721,8 +23125,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -23753,7 +23155,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23814,8 +23215,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -23876,8 +23275,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -23908,7 +23305,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -23969,8 +23365,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -24001,7 +23395,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -24027,7 +23420,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -24093,7 +23485,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -24129,7 +23520,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -24160,7 +23550,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -24191,7 +23580,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -24257,7 +23645,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -24288,7 +23675,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -24354,7 +23740,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -24450,8 +23835,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -24482,7 +23865,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -24513,7 +23895,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -24574,8 +23955,6 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -24606,7 +23985,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -24637,7 +24015,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -24668,7 +24045,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -24699,7 +24075,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -24725,7 +24100,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Ups and downs need to be understood — talk to student directly.</t>
@@ -24761,7 +24135,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24792,7 +24165,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24893,7 +24265,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24924,7 +24295,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24955,7 +24325,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24986,7 +24355,6 @@
           <t>Prose - The Portrait of a Lady</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -25017,7 +24385,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25043,8 +24410,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25070,7 +24435,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -25101,8 +24465,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -25128,7 +24490,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -25164,7 +24525,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -25195,7 +24555,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -25221,8 +24580,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -25248,8 +24605,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25275,8 +24630,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -25307,7 +24660,6 @@
           <t>Grammar &amp; Composition</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25338,7 +24690,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25369,7 +24720,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -25395,8 +24745,6 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -25427,7 +24775,6 @@
           <t>Poetry - Ode to Autumn</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -25453,8 +24800,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25480,7 +24825,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Inconsistent results — strong in some tests, weak in others.</t>
@@ -25511,7 +24855,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Ups and downs need to be understood — talk to student directly.</t>
@@ -25542,7 +24885,6 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -25680,8 +25022,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25712,7 +25052,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25738,8 +25077,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25765,8 +25102,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25797,7 +25132,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25828,7 +25162,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25854,8 +25187,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25881,8 +25212,6 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25908,8 +25237,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25940,7 +25267,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25966,8 +25292,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25998,7 +25322,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -26029,7 +25352,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -26055,8 +25377,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -26082,8 +25402,6 @@
       <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -26109,8 +25427,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -26141,7 +25457,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -26172,7 +25487,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -26198,7 +25512,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Visible improvement — the extra effort is showing results.</t>
@@ -26229,7 +25542,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -26265,7 +25577,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -26296,7 +25607,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -26362,7 +25672,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -26423,8 +25732,6 @@
       <c r="G27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -26455,7 +25762,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -26521,7 +25827,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -26552,7 +25857,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26583,7 +25887,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26609,7 +25912,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -26675,8 +25977,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26702,8 +26002,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26734,7 +26032,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26765,7 +26062,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26796,7 +26092,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26827,7 +26122,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26858,7 +26152,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26884,7 +26177,6 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Needs urgent academic support, at risk of failing.</t>
@@ -26915,8 +26207,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26947,7 +26237,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -26973,8 +26262,6 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -27040,7 +26327,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -27066,8 +26352,6 @@
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -27098,7 +26382,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -27129,7 +26412,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27155,8 +26437,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27217,7 +26497,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Exceptional performance, keep up this standard.</t>
@@ -27288,7 +26567,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -27314,8 +26592,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -27376,7 +26652,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -27412,7 +26687,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27443,7 +26717,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27469,8 +26742,6 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -27496,8 +26767,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27528,7 +26797,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -27594,7 +26862,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -27625,7 +26892,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -27691,7 +26957,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -27717,7 +26982,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -27748,8 +27012,6 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -27780,7 +27042,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -27811,7 +27072,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -27837,8 +27097,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -27869,7 +27127,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27900,7 +27157,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -27961,8 +27217,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -27993,7 +27247,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -28024,7 +27277,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -28055,7 +27307,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -28081,8 +27332,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -28113,7 +27362,6 @@
           <t>Biotechnology</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -28144,7 +27392,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -28170,8 +27417,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -28237,7 +27482,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -28268,7 +27512,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -28299,7 +27542,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -28330,7 +27572,6 @@
           <t>Genetics &amp; Evolution</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -28356,7 +27597,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
@@ -28392,7 +27632,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28423,7 +27662,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28454,7 +27692,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28480,8 +27717,6 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28507,8 +27742,6 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -28574,7 +27807,6 @@
           <t>Ecology</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -28635,8 +27867,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -28667,7 +27897,6 @@
           <t>Reproduction in Organisms</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -28805,7 +28034,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28836,7 +28064,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28867,7 +28094,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28928,7 +28154,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -28959,8 +28184,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29061,7 +28284,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29127,7 +28349,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29158,7 +28379,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29189,7 +28409,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29220,7 +28439,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29251,7 +28469,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29277,8 +28494,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29304,8 +28519,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29331,7 +28544,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -29367,7 +28579,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -29398,7 +28609,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -29424,8 +28634,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -29456,7 +28664,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -29482,8 +28689,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -29514,7 +28719,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -29575,8 +28779,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -29607,7 +28809,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -29633,8 +28834,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -29730,8 +28929,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -29762,7 +28959,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -29828,7 +29024,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -29859,7 +29054,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -29885,8 +29079,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -29917,7 +29109,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -29948,7 +29139,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -29979,7 +29169,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -30010,7 +29199,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -30041,7 +29229,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -30072,7 +29259,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -30098,8 +29284,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -30130,7 +29314,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -30196,7 +29379,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -30227,7 +29409,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -30258,7 +29439,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -30284,8 +29464,6 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -30316,7 +29494,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -30347,7 +29524,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -30413,7 +29589,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -30439,8 +29614,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -30506,7 +29679,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -30602,8 +29774,6 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -30634,7 +29804,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -30700,7 +29869,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -30731,7 +29899,6 @@
           <t>EM Induction</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -30832,7 +29999,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -30863,7 +30029,6 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -30894,7 +30059,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -30925,7 +30089,6 @@
           <t>Optics</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -30951,7 +30114,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Needs attention — performance has slipped recently.</t>
@@ -30982,7 +30144,6 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -31013,8 +30174,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -31040,8 +30199,6 @@
       <c r="G74" t="n">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -31102,7 +30259,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -31138,7 +30294,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -31169,7 +30324,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -31200,7 +30354,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -31231,7 +30384,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -31262,7 +30414,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -31288,7 +30439,6 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -31324,7 +30474,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -31350,8 +30499,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -31412,8 +30559,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -31444,7 +30589,6 @@
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -31470,7 +30614,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -31501,8 +30644,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -31533,7 +30674,6 @@
           <t>Current Electricity</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -31559,8 +30699,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -31621,8 +30759,6 @@
       <c r="G93" t="n">
         <v>1</v>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -31648,8 +30784,6 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -31715,7 +30849,6 @@
           <t>Magnetic Effects</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -31741,7 +30874,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Noticeable drop in performance, please check in at home.</t>
@@ -31772,8 +30904,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -31799,8 +30929,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -31826,8 +30954,6 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -31965,7 +31091,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32031,7 +31156,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32062,7 +31186,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32093,7 +31216,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32124,7 +31246,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32155,7 +31276,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32181,8 +31301,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32248,7 +31366,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32279,7 +31396,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32310,7 +31426,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32341,7 +31456,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32367,8 +31481,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -32399,7 +31511,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32500,7 +31611,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32531,7 +31641,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -32597,7 +31706,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -32623,8 +31731,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -32655,7 +31761,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -32686,7 +31791,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -32752,7 +31856,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -32783,7 +31886,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -32814,7 +31916,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -32840,8 +31941,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -32872,7 +31971,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -32903,7 +32001,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -32929,8 +32026,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -32961,7 +32056,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -32987,8 +32081,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -33019,7 +32111,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -33045,8 +32136,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -33072,8 +32161,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -33104,7 +32191,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -33135,7 +32221,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -33236,7 +32321,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -33302,7 +32386,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -33333,7 +32416,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -33359,8 +32441,6 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -33391,7 +32471,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -33417,8 +32496,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -33449,7 +32526,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -33475,8 +32551,6 @@
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -33502,8 +32576,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -33604,7 +32676,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -33630,8 +32701,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -33657,8 +32726,6 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -33684,8 +32751,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -33711,7 +32776,6 @@
       <c r="G59" t="n">
         <v>1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -33747,7 +32811,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -33773,8 +32836,6 @@
       <c r="G61" t="n">
         <v>2</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -33805,7 +32866,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -33836,7 +32896,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -33862,8 +32921,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -33889,7 +32946,6 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Struggling with fundamentals, needs remedial sessions.</t>
@@ -33925,7 +32981,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -33986,7 +33041,6 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Needs urgent academic support, at risk of failing.</t>
@@ -34017,8 +33071,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -34084,7 +33136,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -34110,8 +33161,6 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -34137,8 +33186,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -34169,7 +33216,6 @@
           <t>Electrochemistry</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -34200,7 +33246,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -34231,7 +33276,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -34262,7 +33306,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -34293,7 +33336,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -34324,7 +33366,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -34350,7 +33391,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -34456,7 +33496,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -34517,8 +33556,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -34549,7 +33586,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -34610,8 +33646,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -34642,7 +33676,6 @@
           <t>Coordination Compounds</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -34668,8 +33701,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -34695,8 +33726,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -34727,7 +33756,6 @@
           <t>Solutions</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -34758,7 +33786,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -34789,7 +33816,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -34820,7 +33846,6 @@
           <t>Solid State</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -34846,7 +33871,6 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Needs attention — performance has slipped recently.</t>
@@ -34917,7 +33941,6 @@
           <t>Chemical Kinetics</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -34943,7 +33966,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Unpredictable performance, may help to identify what's different on good days.</t>
@@ -34979,7 +34001,6 @@
           <t>p-Block Elements</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -35005,7 +34026,6 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
